--- a/ig/test-tabs-svs/ValueSet-jdv-j328-public-activite-smsse-regulee-finess.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j328-public-activite-smsse-regulee-finess.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="310">
   <si>
     <t>Property</t>
   </si>
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r403-public-activite-smsse-regulee|20260223120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r403-public-activite-smsse-regulee|20260629120000</t>
   </si>
   <si>
     <t>version</t>
@@ -167,6 +167,12 @@
     <t>Adolescents ASE (7-17 ans)</t>
   </si>
   <si>
+    <t>842</t>
+  </si>
+  <si>
+    <t>Adultes (sans autre indication)</t>
+  </si>
+  <si>
     <t>441</t>
   </si>
   <si>
@@ -401,6 +407,12 @@
     <t>Enfants d'Age Préscolaire</t>
   </si>
   <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>Enfants et adolescents (sans autre indication)</t>
+  </si>
+  <si>
     <t>807</t>
   </si>
   <si>
@@ -569,6 +581,12 @@
     <t>Parents en difficulté avec enfant</t>
   </si>
   <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>Patients de soins sans consentement</t>
+  </si>
+  <si>
     <t>834</t>
   </si>
   <si>
@@ -759,6 +777,12 @@
   </si>
   <si>
     <t>Prostituées avec ou sans Enfant</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>Périnatalité</t>
   </si>
   <si>
     <t>999</t>
@@ -1270,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1587,7 +1611,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1629,7 +1653,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -1692,7 +1716,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1797,7 +1821,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1818,7 +1842,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1902,7 +1926,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -1923,7 +1947,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1944,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1986,7 +2010,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -2049,7 +2073,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -2070,7 +2094,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -2133,7 +2157,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
@@ -2490,7 +2514,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -2511,7 +2535,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -2553,7 +2577,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
@@ -2574,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63">
@@ -2679,7 +2703,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -2700,7 +2724,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -2721,7 +2745,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
@@ -2742,7 +2766,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -2826,7 +2850,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
@@ -2910,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
@@ -2931,7 +2955,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
@@ -2952,7 +2976,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -2973,7 +2997,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
@@ -2994,7 +3018,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -3330,7 +3354,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -3351,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
@@ -3372,7 +3396,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101">
@@ -3414,7 +3438,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103">
@@ -3477,7 +3501,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
@@ -3498,7 +3522,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107">
@@ -3624,7 +3648,7 @@
         <v>15</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113">
@@ -3666,7 +3690,7 @@
         <v>15</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115">
@@ -3729,7 +3753,7 @@
         <v>15</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118">
@@ -3792,7 +3816,7 @@
         <v>15</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121">
@@ -3855,7 +3879,7 @@
         <v>15</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124">
@@ -3897,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
@@ -3918,7 +3942,7 @@
         <v>15</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
@@ -3960,7 +3984,7 @@
         <v>15</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129">
@@ -3981,6 +4005,90 @@
         <v>15</v>
       </c>
       <c r="G129" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="F130" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="F131" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="F132" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="F133" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G133" t="s" s="2">
         <v>15</v>
       </c>
     </row>
